--- a/exports/trend_1d/VBL_full_report.xlsx
+++ b/exports/trend_1d/VBL_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q65"/>
+  <dimension ref="A1:U65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>16.1</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42725</v>
+        <v>42726</v>
       </c>
       <c r="H2" t="n">
-        <v>23.55</v>
+        <v>22.75</v>
       </c>
       <c r="I2" t="n">
         <v>22.9607470862</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K2" t="n">
-        <v>-10.29</v>
+        <v>-13.33</v>
       </c>
       <c r="L2" t="n">
-        <v>10.67</v>
+        <v>18.29</v>
       </c>
       <c r="M2" t="n">
         <v>2.44</v>
       </c>
       <c r="N2" t="n">
-        <v>3.19</v>
+        <v>3.4</v>
       </c>
       <c r="O2" t="n">
         <v>0.57</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,25 +626,25 @@
         <v>11.18</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42737</v>
+        <v>42738</v>
       </c>
       <c r="H3" t="n">
-        <v>23.65</v>
+        <v>24.3</v>
       </c>
       <c r="I3" t="n">
         <v>24.19759467182523</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K3" t="n">
-        <v>-3.96</v>
+        <v>-6.81</v>
       </c>
       <c r="L3" t="n">
-        <v>4.18</v>
+        <v>9.23</v>
       </c>
       <c r="M3" t="n">
-        <v>1.55</v>
+        <v>2.96</v>
       </c>
       <c r="N3" t="n">
         <v>4.88</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>10.65</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42795</v>
+        <v>42796</v>
       </c>
       <c r="H4" t="n">
-        <v>22.85</v>
+        <v>22.3</v>
       </c>
       <c r="I4" t="n">
         <v>22.65870979337892</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K4" t="n">
-        <v>-5.97</v>
+        <v>-8.23</v>
       </c>
       <c r="L4" t="n">
-        <v>7.41</v>
+        <v>8.85</v>
       </c>
       <c r="M4" t="n">
         <v>2.09</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>10.31</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42818</v>
+        <v>42821</v>
       </c>
       <c r="H5" t="n">
-        <v>22.4</v>
+        <v>22.8</v>
       </c>
       <c r="I5" t="n">
         <v>22.77959437996861</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.45</v>
+        <v>-2.24</v>
       </c>
       <c r="L5" t="n">
         <v>3.81</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>10.07</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>43020</v>
+        <v>43021</v>
       </c>
       <c r="H6" t="n">
-        <v>29.75</v>
+        <v>29.5</v>
       </c>
       <c r="I6" t="n">
         <v>29.55772330365549</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K6" t="n">
-        <v>30.48</v>
+        <v>29.39</v>
       </c>
       <c r="L6" t="n">
         <v>2.85</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>137</v>
+        <v>138</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>8</v>
+      </c>
+      <c r="U6" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>9.23</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>43088</v>
+        <v>43089</v>
       </c>
       <c r="H7" t="n">
-        <v>30.75</v>
+        <v>31.75</v>
       </c>
       <c r="I7" t="n">
         <v>31.50698138717683</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K7" t="n">
-        <v>-4.24</v>
+        <v>-7.63</v>
       </c>
       <c r="L7" t="n">
         <v>9.49</v>
@@ -840,7 +923,7 @@
         <v>3.67</v>
       </c>
       <c r="N7" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="O7" t="n">
         <v>-0.84</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>10.55</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>43171</v>
+        <v>43172</v>
       </c>
       <c r="H8" t="n">
-        <v>36.75</v>
+        <v>36.1</v>
       </c>
       <c r="I8" t="n">
         <v>36.41318861618135</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K8" t="n">
-        <v>15.75</v>
+        <v>13.7</v>
       </c>
       <c r="L8" t="n">
         <v>3.62</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>13.46</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>43220</v>
+        <v>43222</v>
       </c>
       <c r="H9" t="n">
-        <v>38.75</v>
+        <v>39.55</v>
       </c>
       <c r="I9" t="n">
         <v>39.54585953976625</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K9" t="n">
-        <v>-7.34</v>
+        <v>-9.56</v>
       </c>
       <c r="L9" t="n">
-        <v>11.63</v>
+        <v>11.91</v>
       </c>
       <c r="M9" t="n">
         <v>1.07</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>8.94</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>43306</v>
+        <v>43307</v>
       </c>
       <c r="H10" t="n">
-        <v>41.3</v>
+        <v>40.85</v>
       </c>
       <c r="I10" t="n">
         <v>41.11014929683981</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K10" t="n">
-        <v>4.42</v>
+        <v>3.29</v>
       </c>
       <c r="L10" t="n">
         <v>2.02</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>10.13</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>43319</v>
+        <v>43320</v>
       </c>
       <c r="H11" t="n">
-        <v>43.95</v>
+        <v>45.2</v>
       </c>
       <c r="I11" t="n">
         <v>44.98890962371765</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K11" t="n">
-        <v>-7.59</v>
+        <v>-10.65</v>
       </c>
       <c r="L11" t="n">
         <v>12.97</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>11.6</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>43370</v>
+        <v>43371</v>
       </c>
       <c r="H12" t="n">
-        <v>45.05</v>
+        <v>43.8</v>
       </c>
       <c r="I12" t="n">
         <v>44.51659856425127</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.33</v>
+        <v>-3.1</v>
       </c>
       <c r="L12" t="n">
         <v>10.07</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>15.83</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>43462</v>
+        <v>43465</v>
       </c>
       <c r="H13" t="n">
-        <v>44.9</v>
+        <v>46.5</v>
       </c>
       <c r="I13" t="n">
         <v>46.20519822514304</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.51</v>
+        <v>-6.16</v>
       </c>
       <c r="L13" t="n">
         <v>14.38</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>11.94</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>43488</v>
+        <v>43489</v>
       </c>
       <c r="H14" t="n">
-        <v>46.25</v>
+        <v>45.35</v>
       </c>
       <c r="I14" t="n">
         <v>45.50649207621122</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.54</v>
+        <v>-2.47</v>
       </c>
       <c r="L14" t="n">
         <v>4.19</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>8.43</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43496</v>
+        <v>43497</v>
       </c>
       <c r="H15" t="n">
-        <v>48.65</v>
+        <v>49.4</v>
       </c>
       <c r="I15" t="n">
         <v>49.17500274391804</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K15" t="n">
-        <v>-7.28</v>
+        <v>-8.93</v>
       </c>
       <c r="L15" t="n">
-        <v>9.81</v>
+        <v>10.8</v>
       </c>
       <c r="M15" t="n">
         <v>0.66</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>8.380000000000001</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43508</v>
+        <v>43509</v>
       </c>
       <c r="H16" t="n">
-        <v>45.6</v>
+        <v>45.2</v>
       </c>
       <c r="I16" t="n">
         <v>45.25957216676946</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K16" t="n">
-        <v>-7.69</v>
+        <v>-8.5</v>
       </c>
       <c r="L16" t="n">
         <v>9.92</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>12.25</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43552</v>
+        <v>43553</v>
       </c>
       <c r="H17" t="n">
-        <v>48.15</v>
+        <v>51.35</v>
       </c>
       <c r="I17" t="n">
         <v>49.98869406313494</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K17" t="n">
-        <v>-6.53</v>
+        <v>-13.61</v>
       </c>
       <c r="L17" t="n">
-        <v>8.85</v>
+        <v>14.93</v>
       </c>
       <c r="M17" t="n">
-        <v>1.15</v>
+        <v>2.49</v>
       </c>
       <c r="N17" t="n">
-        <v>2.68</v>
+        <v>6.65</v>
       </c>
       <c r="O17" t="n">
         <v>-0.88</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>9.24</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43565</v>
+        <v>43566</v>
       </c>
       <c r="H18" t="n">
-        <v>50.95</v>
+        <v>50.3</v>
       </c>
       <c r="I18" t="n">
         <v>50.48095378692724</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.78</v>
+        <v>-2.04</v>
       </c>
       <c r="L18" t="n">
         <v>3.89</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>9.99</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43587</v>
+        <v>43588</v>
       </c>
       <c r="H19" t="n">
-        <v>52.35</v>
+        <v>53.6</v>
       </c>
       <c r="I19" t="n">
         <v>52.80713297163506</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K19" t="n">
-        <v>-4.08</v>
+        <v>-6.56</v>
       </c>
       <c r="L19" t="n">
-        <v>5.57</v>
+        <v>7.75</v>
       </c>
       <c r="M19" t="n">
         <v>1.02</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>8.77</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43630</v>
+        <v>43633</v>
       </c>
       <c r="H20" t="n">
-        <v>55.1</v>
+        <v>50.9</v>
       </c>
       <c r="I20" t="n">
         <v>52.13672950082407</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K20" t="n">
-        <v>2.8</v>
+        <v>-5.04</v>
       </c>
       <c r="L20" t="n">
-        <v>2.71</v>
+        <v>12.41</v>
       </c>
       <c r="M20" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>2.5</v>
+        <v>7.62</v>
       </c>
       <c r="O20" t="n">
         <v>2.39</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>12.18</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43654</v>
+        <v>43655</v>
       </c>
       <c r="H21" t="n">
-        <v>56.9</v>
+        <v>57.2</v>
       </c>
       <c r="I21" t="n">
         <v>57.1014991043325</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K21" t="n">
-        <v>-11.79</v>
+        <v>-12.38</v>
       </c>
       <c r="L21" t="n">
-        <v>12.97</v>
+        <v>13.46</v>
       </c>
       <c r="M21" t="n">
         <v>3.34</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>8.279999999999999</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43669</v>
+        <v>43670</v>
       </c>
       <c r="H22" t="n">
-        <v>55.95</v>
+        <v>52.6</v>
       </c>
       <c r="I22" t="n">
         <v>52.78325096475363</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.19</v>
+        <v>-8.039999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>7.78</v>
+        <v>19.76</v>
       </c>
       <c r="M22" t="n">
         <v>2.02</v>
       </c>
       <c r="N22" t="n">
-        <v>2.5</v>
+        <v>5.99</v>
       </c>
       <c r="O22" t="n">
         <v>0.53</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>13.03</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43773</v>
+        <v>43774</v>
       </c>
       <c r="H23" t="n">
-        <v>56.2</v>
+        <v>62.4</v>
       </c>
       <c r="I23" t="n">
         <v>59.45461839847269</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K23" t="n">
-        <v>-6.84</v>
+        <v>-18.63</v>
       </c>
       <c r="L23" t="n">
-        <v>13.88</v>
+        <v>22.91</v>
       </c>
       <c r="M23" t="n">
         <v>3.04</v>
       </c>
       <c r="N23" t="n">
-        <v>6.39</v>
+        <v>11.03</v>
       </c>
       <c r="O23" t="n">
         <v>-5.99</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>5</v>
+      </c>
+      <c r="U23" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>13.69</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43859</v>
+        <v>43860</v>
       </c>
       <c r="H24" t="n">
-        <v>71.84999999999999</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="I24" t="n">
         <v>69.5348499461234</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K24" t="n">
-        <v>15.14</v>
+        <v>7.53</v>
       </c>
       <c r="L24" t="n">
         <v>8.41</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>17.16</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43999</v>
+        <v>44000</v>
       </c>
       <c r="H25" t="n">
-        <v>58.8</v>
+        <v>62.85</v>
       </c>
       <c r="I25" t="n">
         <v>60.35434966719652</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K25" t="n">
-        <v>12.37</v>
+        <v>6.33</v>
       </c>
       <c r="L25" t="n">
         <v>14.31</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>5</v>
+      </c>
+      <c r="U25" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>17.32</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>44092</v>
+        <v>44095</v>
       </c>
       <c r="H26" t="n">
-        <v>62.7</v>
+        <v>61.35</v>
       </c>
       <c r="I26" t="n">
         <v>61.71618123572359</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.24</v>
+        <v>-2.39</v>
       </c>
       <c r="L26" t="n">
         <v>6.92</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>11.16</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>44144</v>
+        <v>44145</v>
       </c>
       <c r="H27" t="n">
-        <v>61.5</v>
+        <v>64.45</v>
       </c>
       <c r="I27" t="n">
         <v>62.75820870888192</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.24</v>
+        <v>-5.05</v>
       </c>
       <c r="L27" t="n">
-        <v>4.97</v>
+        <v>5.7</v>
       </c>
       <c r="M27" t="n">
         <v>1.78</v>
       </c>
       <c r="N27" t="n">
-        <v>3.85</v>
+        <v>4.8</v>
       </c>
       <c r="O27" t="n">
         <v>-2.15</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>11.06</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>44210</v>
+        <v>44211</v>
       </c>
       <c r="H28" t="n">
-        <v>81</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="I28" t="n">
         <v>80.2778654218596</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K28" t="n">
-        <v>25.68</v>
+        <v>23.51</v>
       </c>
       <c r="L28" t="n">
         <v>4.81</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>15.7</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>44246</v>
+        <v>44249</v>
       </c>
       <c r="H29" t="n">
-        <v>86.59999999999999</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="I29" t="n">
         <v>88.49481126063183</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K29" t="n">
-        <v>-8.789999999999999</v>
+        <v>-14.45</v>
       </c>
       <c r="L29" t="n">
-        <v>9.67</v>
+        <v>20.04</v>
       </c>
       <c r="M29" t="n">
         <v>1.37</v>
       </c>
       <c r="N29" t="n">
-        <v>4.89</v>
+        <v>5.2</v>
       </c>
       <c r="O29" t="n">
         <v>-1.73</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>12.66</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44306</v>
+        <v>44308</v>
       </c>
       <c r="H30" t="n">
-        <v>82.34999999999999</v>
+        <v>79.15000000000001</v>
       </c>
       <c r="I30" t="n">
         <v>81.56126597672399</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K30" t="n">
-        <v>-9.6</v>
+        <v>-13.12</v>
       </c>
       <c r="L30" t="n">
-        <v>10.21</v>
+        <v>13.56</v>
       </c>
       <c r="M30" t="n">
         <v>1.67</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>13.61</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44316</v>
+        <v>44319</v>
       </c>
       <c r="H31" t="n">
-        <v>84.5</v>
+        <v>89.25</v>
       </c>
       <c r="I31" t="n">
         <v>88.21218909617249</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K31" t="n">
-        <v>-6.76</v>
+        <v>-12.76</v>
       </c>
       <c r="L31" t="n">
-        <v>11.75</v>
+        <v>14.28</v>
       </c>
       <c r="M31" t="n">
         <v>5.43</v>
       </c>
       <c r="N31" t="n">
-        <v>3.69</v>
+        <v>5.62</v>
       </c>
       <c r="O31" t="n">
         <v>-3.89</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>14.17</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44370</v>
+        <v>44371</v>
       </c>
       <c r="H32" t="n">
-        <v>100.45</v>
+        <v>96.2</v>
       </c>
       <c r="I32" t="n">
         <v>98.3362725668452</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K32" t="n">
-        <v>12.55</v>
+        <v>7.79</v>
       </c>
       <c r="L32" t="n">
         <v>4.26</v>
@@ -2265,7 +2648,7 @@
         <v>1.43</v>
       </c>
       <c r="N32" t="n">
-        <v>3.13</v>
+        <v>4.23</v>
       </c>
       <c r="O32" t="n">
         <v>5.62</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>14.45</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44389</v>
+        <v>44390</v>
       </c>
       <c r="H33" t="n">
-        <v>104.15</v>
+        <v>104.9</v>
       </c>
       <c r="I33" t="n">
         <v>104.863304880512</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K33" t="n">
-        <v>-8.26</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>8.42</v>
+        <v>11.43</v>
       </c>
       <c r="M33" t="n">
         <v>0.93</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>7.57</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44488</v>
+        <v>44489</v>
       </c>
       <c r="H34" t="n">
-        <v>120.6</v>
+        <v>113.4</v>
       </c>
       <c r="I34" t="n">
         <v>113.9671119744886</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K34" t="n">
-        <v>14.97</v>
+        <v>8.1</v>
       </c>
       <c r="L34" t="n">
         <v>8.390000000000001</v>
@@ -2379,7 +2786,7 @@
         <v>0.99</v>
       </c>
       <c r="N34" t="n">
-        <v>5.54</v>
+        <v>5.97</v>
       </c>
       <c r="O34" t="n">
         <v>0.72</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>4</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>12.43</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44498</v>
+        <v>44501</v>
       </c>
       <c r="H35" t="n">
-        <v>113.25</v>
+        <v>122.85</v>
       </c>
       <c r="I35" t="n">
         <v>120.3842994062014</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K35" t="n">
-        <v>0.13</v>
+        <v>-8.33</v>
       </c>
       <c r="L35" t="n">
-        <v>6.88</v>
+        <v>9.35</v>
       </c>
       <c r="M35" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="N35" t="n">
-        <v>3.14</v>
+        <v>8.48</v>
       </c>
       <c r="O35" t="n">
         <v>-5.97</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>14.46</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44547</v>
+        <v>44550</v>
       </c>
       <c r="H36" t="n">
-        <v>115.5</v>
+        <v>110.35</v>
       </c>
       <c r="I36" t="n">
         <v>115.2623245413078</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K36" t="n">
-        <v>-5.98</v>
+        <v>-10.18</v>
       </c>
       <c r="L36" t="n">
-        <v>8.470000000000001</v>
+        <v>10.99</v>
       </c>
       <c r="M36" t="n">
-        <v>0.82</v>
+        <v>0.95</v>
       </c>
       <c r="N36" t="n">
-        <v>4.05</v>
+        <v>4.46</v>
       </c>
       <c r="O36" t="n">
         <v>8.48</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>12.55</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44574</v>
+        <v>44575</v>
       </c>
       <c r="H37" t="n">
-        <v>120.75</v>
+        <v>123.8</v>
       </c>
       <c r="I37" t="n">
         <v>122.9254916852463</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K37" t="n">
-        <v>-9.42</v>
+        <v>-12.19</v>
       </c>
       <c r="L37" t="n">
-        <v>11.15</v>
+        <v>12.37</v>
       </c>
       <c r="M37" t="n">
         <v>2.37</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>11.67</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44792</v>
+        <v>44795</v>
       </c>
       <c r="H38" t="n">
-        <v>197.65</v>
+        <v>183.95</v>
       </c>
       <c r="I38" t="n">
         <v>187.1633644473388</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="K38" t="n">
-        <v>59.65</v>
+        <v>48.59</v>
       </c>
       <c r="L38" t="n">
         <v>8.970000000000001</v>
@@ -2607,7 +3062,7 @@
         <v>3.99</v>
       </c>
       <c r="N38" t="n">
-        <v>5.37</v>
+        <v>6.93</v>
       </c>
       <c r="O38" t="n">
         <v>2.53</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>148</v>
+        <v>149</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>8</v>
+      </c>
+      <c r="U38" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>17.61</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44809</v>
+        <v>44810</v>
       </c>
       <c r="H39" t="n">
-        <v>206.7</v>
+        <v>218.75</v>
       </c>
       <c r="I39" t="n">
         <v>215.18425731789</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K39" t="n">
-        <v>-12.37</v>
+        <v>-18.92</v>
       </c>
       <c r="L39" t="n">
-        <v>14.27</v>
+        <v>19.9</v>
       </c>
       <c r="M39" t="n">
         <v>1.41</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>14.58</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44831</v>
+        <v>44832</v>
       </c>
       <c r="H40" t="n">
-        <v>207.7</v>
+        <v>205.95</v>
       </c>
       <c r="I40" t="n">
         <v>207.3991519246089</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K40" t="n">
-        <v>-5.05</v>
+        <v>-5.85</v>
       </c>
       <c r="L40" t="n">
         <v>6.47</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>14.08</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44866</v>
+        <v>44867</v>
       </c>
       <c r="H41" t="n">
-        <v>221.4</v>
+        <v>225.5</v>
       </c>
       <c r="I41" t="n">
         <v>225.1654615179185</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K41" t="n">
-        <v>-7.5</v>
+        <v>-9.49</v>
       </c>
       <c r="L41" t="n">
-        <v>12.16</v>
+        <v>13.13</v>
       </c>
       <c r="M41" t="n">
         <v>2.31</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>10.06</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44936</v>
+        <v>44937</v>
       </c>
       <c r="H42" t="n">
-        <v>257.45</v>
+        <v>245</v>
       </c>
       <c r="I42" t="n">
         <v>246.132614533971</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K42" t="n">
-        <v>14.17</v>
+        <v>8.65</v>
       </c>
       <c r="L42" t="n">
         <v>4.61</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>15.83</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44963</v>
+        <v>44964</v>
       </c>
       <c r="H43" t="n">
-        <v>244.35</v>
+        <v>260.8</v>
       </c>
       <c r="I43" t="n">
         <v>256.7156604615666</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K43" t="n">
-        <v>0.27</v>
+        <v>-6.45</v>
       </c>
       <c r="L43" t="n">
-        <v>5.65</v>
+        <v>7.33</v>
       </c>
       <c r="M43" t="n">
         <v>1.16</v>
       </c>
       <c r="N43" t="n">
-        <v>6.32</v>
+        <v>6.73</v>
       </c>
       <c r="O43" t="n">
         <v>-4.84</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>15.52</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45099</v>
+        <v>45100</v>
       </c>
       <c r="H44" t="n">
-        <v>321.4</v>
+        <v>306.45</v>
       </c>
       <c r="I44" t="n">
         <v>311.2414987791121</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K44" t="n">
-        <v>23.24</v>
+        <v>17.5</v>
       </c>
       <c r="L44" t="n">
         <v>6.06</v>
@@ -2949,7 +3476,7 @@
         <v>2.73</v>
       </c>
       <c r="N44" t="n">
-        <v>4.16</v>
+        <v>4.65</v>
       </c>
       <c r="O44" t="n">
         <v>6.73</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>5</v>
+      </c>
+      <c r="U44" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>13.27</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45149</v>
+        <v>45152</v>
       </c>
       <c r="H45" t="n">
-        <v>339.75</v>
+        <v>347.25</v>
       </c>
       <c r="I45" t="n">
         <v>343.8738604410459</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K45" t="n">
-        <v>-10.87</v>
+        <v>-13.31</v>
       </c>
       <c r="L45" t="n">
-        <v>11.6</v>
+        <v>13.82</v>
       </c>
       <c r="M45" t="n">
         <v>1.49</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>9.49</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45222</v>
+        <v>45224</v>
       </c>
       <c r="H46" t="n">
-        <v>369.1</v>
+        <v>353.7</v>
       </c>
       <c r="I46" t="n">
         <v>360.8113119642229</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K46" t="n">
-        <v>6.29</v>
+        <v>1.86</v>
       </c>
       <c r="L46" t="n">
         <v>3.96</v>
@@ -3063,7 +3614,7 @@
         <v>1.49</v>
       </c>
       <c r="N46" t="n">
-        <v>2.2</v>
+        <v>4.17</v>
       </c>
       <c r="O46" t="n">
         <v>2.21</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,25 +3662,25 @@
         <v>9.369999999999999</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45232</v>
+        <v>45233</v>
       </c>
       <c r="H47" t="n">
-        <v>370.45</v>
+        <v>380.75</v>
       </c>
       <c r="I47" t="n">
         <v>372.8331360712376</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K47" t="n">
-        <v>-4.74</v>
+        <v>-7.65</v>
       </c>
       <c r="L47" t="n">
-        <v>6.02</v>
+        <v>8.1</v>
       </c>
       <c r="M47" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="N47" t="n">
         <v>5.62</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>9.35</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="H48" t="n">
-        <v>586.8</v>
+        <v>559.15</v>
       </c>
       <c r="I48" t="n">
         <v>567.9458018087263</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K48" t="n">
-        <v>54.12</v>
+        <v>46.85</v>
       </c>
       <c r="L48" t="n">
         <v>2.71</v>
@@ -3177,7 +3752,7 @@
         <v>1.62</v>
       </c>
       <c r="N48" t="n">
-        <v>4.51</v>
+        <v>4.71</v>
       </c>
       <c r="O48" t="n">
         <v>2.78</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>4</v>
+      </c>
+      <c r="U48" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>12.71</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45385</v>
+        <v>45386</v>
       </c>
       <c r="H49" t="n">
-        <v>590.35</v>
+        <v>605.8</v>
       </c>
       <c r="I49" t="n">
         <v>601.3731506154106</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K49" t="n">
-        <v>-5.58</v>
+        <v>-8.34</v>
       </c>
       <c r="L49" t="n">
-        <v>6.95</v>
+        <v>10.52</v>
       </c>
       <c r="M49" t="n">
         <v>1.77</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,25 +3869,25 @@
         <v>9.32</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45506</v>
+        <v>45509</v>
       </c>
       <c r="H50" t="n">
-        <v>628.95</v>
+        <v>601.9</v>
       </c>
       <c r="I50" t="n">
         <v>621.2865941445149</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="K50" t="n">
-        <v>3.82</v>
+        <v>-0.64</v>
       </c>
       <c r="L50" t="n">
         <v>12.84</v>
       </c>
       <c r="M50" t="n">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="N50" t="n">
         <v>6.4</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>5</v>
+      </c>
+      <c r="U50" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>11.48</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45525</v>
+        <v>45526</v>
       </c>
       <c r="H51" t="n">
-        <v>618.45</v>
+        <v>637.7</v>
       </c>
       <c r="I51" t="n">
         <v>632.4927101371534</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K51" t="n">
-        <v>-2.75</v>
+        <v>-5.95</v>
       </c>
       <c r="L51" t="n">
-        <v>3.23</v>
+        <v>6.96</v>
       </c>
       <c r="M51" t="n">
         <v>2.53</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>11.04</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45568</v>
+        <v>45569</v>
       </c>
       <c r="H52" t="n">
-        <v>587.75</v>
+        <v>578.9</v>
       </c>
       <c r="I52" t="n">
         <v>581.8972145420253</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K52" t="n">
-        <v>-7.83</v>
+        <v>-9.220000000000001</v>
       </c>
       <c r="L52" t="n">
         <v>13.88</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>12.71</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45625</v>
+        <v>45628</v>
       </c>
       <c r="H53" t="n">
-        <v>621.2</v>
+        <v>632.25</v>
       </c>
       <c r="I53" t="n">
         <v>630.8944082946157</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K53" t="n">
-        <v>-7.31</v>
+        <v>-9.220000000000001</v>
       </c>
       <c r="L53" t="n">
-        <v>10.49</v>
+        <v>11.25</v>
       </c>
       <c r="M53" t="n">
         <v>3.01</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>10.77</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45666</v>
+        <v>45667</v>
       </c>
       <c r="H54" t="n">
-        <v>605.45</v>
+        <v>596.55</v>
       </c>
       <c r="I54" t="n">
         <v>601.456170706674</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K54" t="n">
-        <v>-4.24</v>
+        <v>-5.65</v>
       </c>
       <c r="L54" t="n">
-        <v>5.29</v>
+        <v>6.62</v>
       </c>
       <c r="M54" t="n">
         <v>5.1</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>8.85</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45733</v>
+        <v>45734</v>
       </c>
       <c r="H55" t="n">
-        <v>507.25</v>
+        <v>532.5</v>
       </c>
       <c r="I55" t="n">
         <v>517.6358337959666</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K55" t="n">
-        <v>14.97</v>
+        <v>10.74</v>
       </c>
       <c r="L55" t="n">
         <v>1.04</v>
@@ -3576,7 +4235,7 @@
         <v>1.65</v>
       </c>
       <c r="N55" t="n">
-        <v>4.79</v>
+        <v>4.98</v>
       </c>
       <c r="O55" t="n">
         <v>-1.47</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>13.91</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45784</v>
+        <v>45785</v>
       </c>
       <c r="H56" t="n">
-        <v>512.1</v>
+        <v>488.75</v>
       </c>
       <c r="I56" t="n">
         <v>503.6508692440267</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K56" t="n">
-        <v>-3.83</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="L56" t="n">
         <v>9.42</v>
@@ -3633,7 +4304,7 @@
         <v>9.42</v>
       </c>
       <c r="N56" t="n">
-        <v>4.54</v>
+        <v>4.56</v>
       </c>
       <c r="O56" t="n">
         <v>4.98</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>15.24</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45854</v>
+        <v>45855</v>
       </c>
       <c r="H57" t="n">
-        <v>480.1</v>
+        <v>490.15</v>
       </c>
       <c r="I57" t="n">
         <v>482.4801279559889</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K57" t="n">
-        <v>1.77</v>
+        <v>-0.29</v>
       </c>
       <c r="L57" t="n">
         <v>5.98</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>7.4</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45904</v>
+        <v>45905</v>
       </c>
       <c r="H58" t="n">
-        <v>489.5</v>
+        <v>469.65</v>
       </c>
       <c r="I58" t="n">
         <v>483.3935101035079</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K58" t="n">
-        <v>-0.13</v>
+        <v>-4.18</v>
       </c>
       <c r="L58" t="n">
-        <v>3.47</v>
+        <v>4.42</v>
       </c>
       <c r="M58" t="n">
         <v>1.92</v>
       </c>
       <c r="N58" t="n">
-        <v>3.12</v>
+        <v>4.06</v>
       </c>
       <c r="O58" t="n">
         <v>2.09</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>12.02</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45951</v>
+        <v>45953</v>
       </c>
       <c r="H59" t="n">
-        <v>459.45</v>
+        <v>465.55</v>
       </c>
       <c r="I59" t="n">
         <v>462.9522717678754</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K59" t="n">
-        <v>2.17</v>
+        <v>0.87</v>
       </c>
       <c r="L59" t="n">
         <v>4.96</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>5.69</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46045</v>
+        <v>46049</v>
       </c>
       <c r="H60" t="n">
-        <v>474.1</v>
+        <v>471.65</v>
       </c>
       <c r="I60" t="n">
         <v>471.8062542332879</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K60" t="n">
-        <v>1.84</v>
+        <v>1.31</v>
       </c>
       <c r="L60" t="n">
         <v>5.03</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>4</v>
+      </c>
+      <c r="U60" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>8.210000000000001</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="H61" t="n">
-        <v>422.9</v>
+        <v>431.6</v>
       </c>
       <c r="I61" t="n">
         <v>427.6116599716855</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K61" t="n">
-        <v>10.34</v>
+        <v>8.49</v>
       </c>
       <c r="L61" t="n">
         <v>4.35</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>10.08</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="H62" t="n">
-        <v>512.95</v>
+        <v>504.3</v>
       </c>
       <c r="I62" t="n">
         <v>506.4903803500259</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K62" t="n">
-        <v>18.85</v>
+        <v>16.84</v>
       </c>
       <c r="L62" t="n">
         <v>3.35</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>3</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>10.28</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="H63" t="n">
-        <v>430</v>
+        <v>436.15</v>
       </c>
       <c r="I63" t="n">
         <v>431.4488246179052</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K63" t="n">
-        <v>14.73</v>
+        <v>13.51</v>
       </c>
       <c r="L63" t="n">
         <v>3.87</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>4</v>
+      </c>
+      <c r="U63" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>7.18</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="H64" t="n">
-        <v>420.55</v>
+        <v>408.4</v>
       </c>
       <c r="I64" t="n">
         <v>412.082051911223</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K64" t="n">
-        <v>-3.58</v>
+        <v>-6.36</v>
       </c>
       <c r="L64" t="n">
-        <v>4.77</v>
+        <v>7.86</v>
       </c>
       <c r="M64" t="n">
         <v>0.93</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4149,6 +4928,14 @@
       <c r="Q65" t="n">
         <v>6</v>
       </c>
+      <c r="R65" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8359,7 +9146,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>55.9</v>
+        <v>57.4</v>
       </c>
     </row>
     <row r="6">
@@ -8369,7 +9156,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
@@ -8379,7 +9166,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="8">
@@ -8389,7 +9176,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -8399,7 +9186,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>72.5</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="10">
@@ -8409,7 +9196,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11">
@@ -8449,7 +9236,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.3</v>
+        <v>-1.37</v>
       </c>
     </row>
     <row r="15">
@@ -8459,7 +9246,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7.36</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="16">
@@ -8469,7 +9256,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-2.92</v>
+        <v>-6.6</v>
       </c>
     </row>
     <row r="17">
@@ -8479,7 +9266,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>59.65</v>
+        <v>48.59</v>
       </c>
     </row>
     <row r="18">
@@ -8489,7 +9276,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>38.1</v>
+        <v>30.2</v>
       </c>
     </row>
     <row r="19">
@@ -8499,7 +9286,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7.5</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -8509,7 +9296,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.92</v>
+        <v>8.85</v>
       </c>
     </row>
     <row r="21">
@@ -8519,7 +9306,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14.38</v>
+        <v>22.91</v>
       </c>
     </row>
     <row r="22">
@@ -8529,7 +9316,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23">
@@ -8539,7 +9326,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24">
@@ -8549,7 +9336,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="25">
@@ -8569,7 +9356,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.58</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="27">
@@ -8579,7 +9366,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>8.85</v>
+        <v>11.03</v>
       </c>
     </row>
     <row r="28">
@@ -8589,7 +9376,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29">
